--- a/Traceability.xlsx
+++ b/Traceability.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gupta\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gregg\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45EA0F76-CEC1-4D71-A7FC-5428155F5E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85CCFD43-DA4A-4BF0-BA2E-3AB7A64CF245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="16303" xr2:uid="{B3225BC0-6EC6-40A0-8D39-563A9F340AA3}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="15800" activeTab="2" xr2:uid="{80C0200E-C64C-445D-AA7B-28C71AFAD157}"/>
   </bookViews>
   <sheets>
-    <sheet name="Req-UC" sheetId="1" r:id="rId1"/>
-    <sheet name="Domain Concepts-UC" sheetId="3" r:id="rId2"/>
-    <sheet name="Development" sheetId="2" r:id="rId3"/>
+    <sheet name="REQ-UC" sheetId="1" r:id="rId1"/>
+    <sheet name="Domain Concepts - UC" sheetId="2" r:id="rId2"/>
+    <sheet name="Development" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,82 +38,118 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
-  <si>
-    <t>Req no</t>
-  </si>
-  <si>
-    <t>3.2.?</t>
-  </si>
-  <si>
-    <t>UC1</t>
-  </si>
-  <si>
-    <t>UC2</t>
-  </si>
-  <si>
-    <t>UC3</t>
-  </si>
-  <si>
-    <t>UC4</t>
-  </si>
-  <si>
-    <t>UC5</t>
-  </si>
-  <si>
-    <t>UC6</t>
-  </si>
-  <si>
-    <t>UC7</t>
-  </si>
-  <si>
-    <t>UC8</t>
-  </si>
-  <si>
-    <t>UC9</t>
-  </si>
-  <si>
-    <t>UC10</t>
-  </si>
-  <si>
-    <t>UC11</t>
-  </si>
-  <si>
-    <t>UC12</t>
-  </si>
-  <si>
-    <t>Domain concepts</t>
-  </si>
-  <si>
-    <t>KeyController</t>
-  </si>
-  <si>
-    <t>Classname</t>
-  </si>
-  <si>
-    <t>Domain Concept</t>
-  </si>
-  <si>
-    <t>StatusDisplay</t>
-  </si>
-  <si>
-    <t>KeyCodeEntry</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="34">
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>REQ 1</t>
+  </si>
+  <si>
+    <t>REQ 2</t>
+  </si>
+  <si>
+    <t>REQ 3</t>
+  </si>
+  <si>
+    <t>REQ 4</t>
+  </si>
+  <si>
+    <t>REQ 5</t>
+  </si>
+  <si>
+    <t>REQ 6</t>
+  </si>
+  <si>
+    <t>REQ 7</t>
+  </si>
+  <si>
+    <t>REQ 8</t>
+  </si>
+  <si>
+    <t>REQ 9</t>
+  </si>
+  <si>
+    <t>REQ 10</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>UC 1</t>
+  </si>
+  <si>
+    <t>UC 2</t>
+  </si>
+  <si>
+    <t>UC 3</t>
+  </si>
+  <si>
+    <t>UC 4</t>
+  </si>
+  <si>
+    <t>UC 5</t>
+  </si>
+  <si>
+    <t>UC 6</t>
+  </si>
+  <si>
+    <t>UC 7</t>
+  </si>
+  <si>
+    <t>UC 8</t>
+  </si>
+  <si>
+    <t>UC 9</t>
+  </si>
+  <si>
+    <t>UC 10</t>
+  </si>
+  <si>
+    <t>UC 11</t>
+  </si>
+  <si>
+    <t>UC 12</t>
+  </si>
+  <si>
+    <t>Use Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authenticator </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DashboardDisplay </t>
+  </si>
+  <si>
+    <t>AccountManager</t>
+  </si>
+  <si>
+    <t>ProjManagerHandler</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>PhaseManager</t>
+  </si>
+  <si>
+    <t>DatabaseManager</t>
+  </si>
+  <si>
+    <t>DashboardDisplay</t>
+  </si>
+  <si>
+    <t>Domain Concepts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -139,8 +175,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -156,6 +195,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -474,122 +517,513 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E00D29-C91A-4EB4-A62F-60F0CABE1359}">
-  <dimension ref="A2:M3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A44BDD-BD9F-4F2B-87B6-28B6D4FF49B1}">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3508470C-44CE-46E2-AF84-6C0DFC7F6D09}">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C847421-A205-4FD3-81E7-36B538077CB6}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>19</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -598,26 +1032,46 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E161AF56-296C-4C23-A20A-D65BA24A3DF5}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7D3857-A931-4B2D-ACE3-6E6A622092BA}">
+  <dimension ref="A2:A8"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
